--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_5d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_r2/post_rank_positive_return/staggered_5d/close/close_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.03337851465866093</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.0563655325260195</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2920123055239057</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2434026618268449</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.2215357227071559</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.3157174432843804</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.3627863700669128</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.1917061371813469</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1909024276995753</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.1971783618341818</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>22.75923828497858</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2589154253883403</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.04304884160391276</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.2338417904815329</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1660602946522266</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.280367550811201</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.668210736051482</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.2416574067239098</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.3029351756676018</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.16948724268156</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.8847927324141821</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>22.42899843530891</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.1147463535718436</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.0006507328855857031</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.2182301800613625</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.1709574741814061</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.5409646405948619</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-0.7635581523444585</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>0.08144481814460283</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.2676977876229256</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1534111082696917</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.4452544954602029</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>23.68553150362642</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>-0.02012112587500181</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.1327025405191633</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.276192118728545</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="F5" s="3" t="n">
+        <v>0.1467455336857349</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>0.004375305450868183</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0.007468366891062281</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>-0.9311797556185725</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2825753778640233</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.2142722605758016</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>-0.07411760509277096</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>26.03464401575402</v>
       </c>
     </row>
@@ -639,54 +747,90 @@
         <v>0.2212595747678838</v>
       </c>
       <c r="C6" s="3" t="n">
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-0.002499953230740815</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>0.2651008289499172</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="F6" s="3" t="n">
+        <v>0.1597170649730373</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>0.8588225469670783</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>1.207824278755874</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="I6" s="4" t="n">
+        <v>0.116169493106482</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>0.1975940194281902</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.1609401438922146</v>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>1.165694125808415</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="N6" s="5" t="n">
         <v>25.55946547342572</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1432576646832844</v>
+        <v>0.1450331540301211</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3419414771452124</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.837253958507101</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.170442011798142</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1625191090840661</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3431668183410793</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.2178836299065887</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.8488753633059887</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.186695565259148</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.411898747893397</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.1671835494691665</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.643181119272647</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>23.31957696132804</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.08936647418261978</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.678278354368966</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>23.39371966510271</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>